--- a/data/trans_orig/IP2001-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2001-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38278</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44898</t>
+          <t>44598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44506</t>
+          <t>44854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>51709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86228</t>
+          <t>85989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94848</t>
+          <t>95125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>26087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>39431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77442</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88228</t>
+          <t>87943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79455</t>
+          <t>78761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91785</t>
+          <t>91406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161087</t>
+          <t>160235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176753</t>
+          <t>177072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59157</t>
+          <t>58665</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60304</t>
+          <t>60291</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64687</t>
+          <t>64686</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122164</t>
+          <t>122275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128046</t>
+          <t>128059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63244</t>
+          <t>63255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69147</t>
+          <t>69573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69321</t>
+          <t>69192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75536</t>
+          <t>75539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135266</t>
+          <t>135663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143566</t>
+          <t>143886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13652</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>26217</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34833</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32921</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39324</t>
+          <t>39935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62207</t>
+          <t>61775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72981</t>
+          <t>73234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48785</t>
+          <t>48766</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53686</t>
+          <t>54026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104469</t>
+          <t>105320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109886</t>
+          <t>109891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113124</t>
+          <t>113257</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121015</t>
+          <t>121032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113668</t>
+          <t>113579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>122442</t>
+          <t>122404</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230964</t>
+          <t>230498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>241997</t>
+          <t>241815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26092</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>24957</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>42710</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123512</t>
+          <t>123671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137198</t>
+          <t>136363</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132182</t>
+          <t>132640</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143977</t>
+          <t>144035</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>260807</t>
+          <t>259824</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>277587</t>
+          <t>277577</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43146</t>
+          <t>43502</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>66270</t>
+          <t>66367</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43736</t>
+          <t>43372</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>67227</t>
+          <t>66992</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93664</t>
+          <t>92812</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>124699</t>
+          <t>124278</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>575579</t>
+          <t>575482</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>598703</t>
+          <t>598347</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>610304</t>
+          <t>610539</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>633795</t>
+          <t>634159</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1194682</t>
+          <t>1195103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1225717</t>
+          <t>1226569</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46036</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52122</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46273</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55663</t>
+          <t>55603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95236</t>
+          <t>94727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106522</t>
+          <t>106369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>19172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35471</t>
+          <t>35076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>76281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87268</t>
+          <t>87602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81319</t>
+          <t>81477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93077</t>
+          <t>92326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161153</t>
+          <t>161548</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177068</t>
+          <t>177712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52868</t>
+          <t>53342</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60667</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58512</t>
+          <t>57606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65383</t>
+          <t>65444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115402</t>
+          <t>114964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124849</t>
+          <t>125318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>14437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58303</t>
+          <t>57362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67297</t>
+          <t>67226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63762</t>
+          <t>63202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73143</t>
+          <t>73298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125022</t>
+          <t>125680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138533</t>
+          <t>138416</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27155</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36697</t>
+          <t>36687</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35658</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42998</t>
+          <t>43069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65738</t>
+          <t>65685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77957</t>
+          <t>78213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41054</t>
+          <t>41435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47138</t>
+          <t>47127</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41095</t>
+          <t>41272</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50544</t>
+          <t>50374</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85371</t>
+          <t>85419</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96120</t>
+          <t>95940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>16946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>23986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113636</t>
+          <t>114453</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123317</t>
+          <t>123408</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113748</t>
+          <t>113629</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>124843</t>
+          <t>124623</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231272</t>
+          <t>233444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>245881</t>
+          <t>246509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>139720</t>
+          <t>140171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>150742</t>
+          <t>150784</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>150143</t>
+          <t>149857</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159536</t>
+          <t>159385</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>293729</t>
+          <t>293830</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>307819</t>
+          <t>308336</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51020</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>77399</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53595</t>
+          <t>54990</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>81579</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>109273</t>
+          <t>112165</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>147774</t>
+          <t>147484</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>581822</t>
+          <t>584636</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>608201</t>
+          <t>609957</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>620439</t>
+          <t>619285</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>647269</t>
+          <t>645874</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1212311</t>
+          <t>1212601</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1250812</t>
+          <t>1247920</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23440</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42043</t>
+          <t>42125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51165</t>
+          <t>51111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47964</t>
+          <t>48128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>57318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93679</t>
+          <t>94339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105797</t>
+          <t>106413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>14149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>24311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85809</t>
+          <t>85474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94585</t>
+          <t>94815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93301</t>
+          <t>92935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102948</t>
+          <t>102348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182022</t>
+          <t>181804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>195367</t>
+          <t>194965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>755</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54147</t>
+          <t>54121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60362</t>
+          <t>60367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60793</t>
+          <t>60766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117582</t>
+          <t>118342</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125579</t>
+          <t>125571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19947</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>20411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>21019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52815</t>
+          <t>52011</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63745</t>
+          <t>63676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55763</t>
+          <t>56707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67994</t>
+          <t>68718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112543</t>
+          <t>112973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129093</t>
+          <t>128861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>18194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31842</t>
+          <t>32343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38904</t>
+          <t>38993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38255</t>
+          <t>38209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65379</t>
+          <t>65345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75598</t>
+          <t>75774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42033</t>
+          <t>41373</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48632</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49935</t>
+          <t>49982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>93550</t>
+          <t>94478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101802</t>
+          <t>101881</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24711</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117627</t>
+          <t>117621</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>126428</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118078</t>
+          <t>117344</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127999</t>
+          <t>127506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>238275</t>
+          <t>238489</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>252167</t>
+          <t>252500</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>27744</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25604</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28918</t>
+          <t>28535</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47037</t>
+          <t>47144</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122692</t>
+          <t>121181</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>135449</t>
+          <t>134647</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>133198</t>
+          <t>133220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146262</t>
+          <t>146432</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>260690</t>
+          <t>260583</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>278809</t>
+          <t>279192</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>57351</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83173</t>
+          <t>81317</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>82868</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120256</t>
+          <t>119580</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>155821</t>
+          <t>153733</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>575679</t>
+          <t>577535</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>601487</t>
+          <t>601501</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>616737</t>
+          <t>617521</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>643990</t>
+          <t>644104</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1202636</t>
+          <t>1204724</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1238201</t>
+          <t>1238877</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67324</t>
+          <t>66282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72218</t>
+          <t>72196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72459</t>
+          <t>72840</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141812</t>
+          <t>141611</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148516</t>
+          <t>148505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119493</t>
+          <t>119073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125189</t>
+          <t>125086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107470</t>
+          <t>109157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120350</t>
+          <t>120739</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229463</t>
+          <t>230652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>244437</t>
+          <t>244630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17471</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46986</t>
+          <t>47416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53791</t>
+          <t>53920</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53035</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63184</t>
+          <t>63336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104149</t>
+          <t>105366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115856</t>
+          <t>115925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61461</t>
+          <t>61410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68350</t>
+          <t>68440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62823</t>
+          <t>62558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73671</t>
+          <t>73051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129379</t>
+          <t>128168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140110</t>
+          <t>140038</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29086</t>
+          <t>29213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33356</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31010</t>
+          <t>30981</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37742</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>62601</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70607</t>
+          <t>70346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43281</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49237</t>
+          <t>48820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90354</t>
+          <t>90361</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96776</t>
+          <t>96764</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24989</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36017</t>
+          <t>34483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109061</t>
+          <t>108785</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118102</t>
+          <t>118310</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129868</t>
+          <t>130841</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145155</t>
+          <t>145215</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>241997</t>
+          <t>243531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>260578</t>
+          <t>261240</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122625</t>
+          <t>122572</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128581</t>
+          <t>128590</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147705</t>
+          <t>148240</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154535</t>
+          <t>154542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>274584</t>
+          <t>274506</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>282878</t>
+          <t>282654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57334</t>
+          <t>57977</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58646</t>
+          <t>59127</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>89761</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>615409</t>
+          <t>616395</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>633855</t>
+          <t>634145</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>688650</t>
+          <t>688007</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>712645</t>
+          <t>713267</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1310937</t>
+          <t>1310618</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1341733</t>
+          <t>1341252</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
